--- a/output/pdf_financials_xlsx/CRE.xlsx
+++ b/output/pdf_financials_xlsx/CRE.xlsx
@@ -10574,7 +10574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R122"/>
+  <dimension ref="A1:R136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19991,10 +19991,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Intérêts courus                                 180 271         90 859     Accrued interest</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Exercices clos les 31 août Years ended August</t>
+          <t>Impôts différés                                1 516 907        673 003     Deferred income taxes</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -20033,8 +20037,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L112" s="4" t="n">
-        <v>3.1e-05</v>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -20056,15 +20062,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q112" s="4" t="n">
+        <v>4e-05</v>
+      </c>
+      <c r="R112" s="4" t="n">
+        <v>0.000377</v>
       </c>
     </row>
     <row r="113">
@@ -20075,12 +20077,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>(Retraité /</t>
+          <t>réglementation.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Restated</t>
+          <t>réglementation. enregistré un bénéfice net de 4 064 936 $ (perte nette recorded a net income of $4,064,936 (2024</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -20144,10 +20146,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q113" s="4" t="n">
+        <v>0.124062</v>
       </c>
       <c r="R113" t="inlineStr">
         <is>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>(Retraité /</t>
+          <t>Intérêts courus                                 90 859       150 125      Accrued interest</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2019 note</t>
+          <t>Impôts différés                                673 003       140 460       Deferred income taxes</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -20207,8 +20207,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L114" s="4" t="n">
-        <v>4e-06</v>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -20225,15 +20227,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P114" s="4" t="n">
+        <v>0.000688</v>
+      </c>
+      <c r="Q114" s="4" t="n">
+        <v>0.000935</v>
       </c>
       <c r="R114" t="inlineStr">
         <is>
@@ -20249,12 +20247,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>négociables                                        149 910      (299 941)      marketable securities</t>
+          <t>PRÉSENTATION (suite)                         PRESENTATION (continued)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>négociables                                        149 910      (299 941)      marketable securities</t>
+          <t>PRÉSENTATION (suite)                         PRESENTATION (continued) enregistré une perte nette de 124 062 $ (3 252 760 $ recorded a net loss of $124,062 (2023</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -20293,8 +20291,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L115" s="4" t="n">
-        <v>0.000504</v>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -20311,10 +20311,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P115" s="4" t="n">
+        <v>3.25276</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -20335,12 +20333,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>négociables                                        149 910      (299 941)      marketable securities</t>
+          <t>Intérêts courus                                 150 125          1 849       Accrued interest</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Variation nette des éléments hors caisse du fonds de                                  Net change in non-cash operating working roulement (note 17) (357 332) (627 033) capital items (Note</t>
+          <t>Impôts différés                                 140 460        421 980       Deferred income taxes</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -20379,8 +20377,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L116" s="4" t="n">
-        <v>1.7e-05</v>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -20392,15 +20392,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O116" s="4" t="n">
+        <v>0.000362</v>
+      </c>
+      <c r="P116" s="4" t="n">
+        <v>0.000195</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -20421,12 +20417,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>souscription                                                                              -     7 000 000    stock and warrants</t>
+          <t>PRÉSENTATION (suite)                         PRESENTATION (continued)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Exercices clos les 31 août Years ended August</t>
+          <t>PRÉSENTATION (suite)                         PRESENTATION (continued) enregistré une perte nette de 3 252 760 $ recorded a net loss of $3,252,760 (2022</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -20465,8 +20461,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L117" s="4" t="n">
-        <v>3.1e-05</v>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -20478,10 +20476,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O117" s="4" t="n">
+        <v>6.423205</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -20507,12 +20503,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>(Retraité /</t>
+          <t>Intérêts courus                                    1 849          (3 794)      Accrued interest</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2019 Note</t>
+          <t>Impôts différés                                  421 980        58 999      Deferred income taxes</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -20551,23 +20547,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L118" s="4" t="n">
-        <v>4e-06</v>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N118" s="4" t="n">
+        <v>0.000728</v>
+      </c>
+      <c r="O118" s="4" t="n">
+        <v>2.8e-05</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -20598,7 +20592,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2-   CONTINUITÉ DE L’EXPLOITATION (suite)           2-   GOING CONCERN (continued) enregistré une perte nette de 2 357 082 $ recorded a net loss of $2,357,082 (2018</t>
+          <t>réglementation. enregistré une perte nette de 6 423 205 $ recorded a net loss of $6,423,205 (2021</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -20647,10 +20641,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N119" s="4" t="n">
+        <v>2.274295</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -20681,12 +20673,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>réglementation.</t>
+          <t>Intérêts courus                                             (3 794)        4 411      Accrued interest</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>négatifs   liés  aux   activités  opérationnelles  de        operations of $2,305,526 (2018  - $3,802,537). In août 2019, la Société a un déficit cumulé de cumulated deficit of $31,134,522 (2018</t>
+          <t>Intérêts courus                                             (3 794)        4 411      Accrued interest</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -20730,15 +20722,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M120" s="4" t="n">
+        <v>0.0006890000000000001</v>
+      </c>
+      <c r="N120" s="4" t="n">
+        <v>0.000455</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -20769,12 +20757,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>d’évaluation                                     906 749      1 300 252      assets</t>
+          <t>réglementation.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>d’évaluation                                     906 749      1 300 252      assets</t>
+          <t>réglementation. enregistré une perte nette de 2 274 295 $ recorded a net loss of $2,274,295 (2020</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -20783,11 +20771,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F121" s="4" t="n">
-        <v>0.000318</v>
-      </c>
-      <c r="G121" s="4" t="n">
-        <v>0.000214</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -20814,10 +20806,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M121" s="4" t="n">
+        <v>1.565318</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -20851,14 +20841,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Acquisition d’immobilisations                                 (3 020)                     -      Acquisition of equipment</t>
-        </is>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Acquisition d’immobilisations                                 (3 020)                     -      Acquisition of equipment total</t>
+          <t>Exercices clos les 31 août Years ended August</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -20867,63 +20853,1263 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F122" s="4" t="n">
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>(Retraité /</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>(Retraité /</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2019 note</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>négociables                                        149 910      (299 941)      marketable securities</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>négociables                                        149 910      (299 941)      marketable securities</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>0.000504</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>négociables                                        149 910      (299 941)      marketable securities</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Variation nette des éléments hors caisse du fonds de                                  Net change in non-cash operating working roulement (note 17) (357 332) (627 033) capital items (Note</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="n">
+        <v>1.7e-05</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>souscription                                                                              -     7 000 000    stock and warrants</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Exercices clos les 31 août Years ended August</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>(Retraité /</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2019 Note</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>réglementation.</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2-   CONTINUITÉ DE L’EXPLOITATION (suite)           2-   GOING CONCERN (continued) enregistré une perte nette de 2 357 082 $ recorded a net loss of $2,357,082 (2018</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>réglementation.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>négatifs   liés  aux   activités  opérationnelles  de        operations of $2,305,526 (2018  - $3,802,537). In août 2019, la Société a un déficit cumulé de cumulated deficit of $31,134,522 (2018</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>d’évaluation                                                                      -          467      evaluation assets</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Gain sur vente d'options de propriétés minières          (23 715)      (823 535)    Gain on sales of mining properties</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="n">
+        <v>8.2e-05</v>
+      </c>
+      <c r="J131" s="4" t="n">
+        <v>0.0009790000000000001</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>d’évaluation                                       7 667       906 749      assets</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>d’évaluation                                       7 667       906 749      assets</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>0.000762</v>
+      </c>
+      <c r="H132" s="4" t="n">
+        <v>0.0009120000000000001</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>d’évaluation                                     906 749      1 300 252      assets</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>d’évaluation                                     906 749      1 300 252      assets</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>0.000318</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>0.000214</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Acquisition d’immobilisations                                 (3 020)                     -      Acquisition of equipment</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Acquisition d’immobilisations                                 (3 020)                     -      Acquisition of equipment total</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="n">
         <v>0.000687</v>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G134" s="4" t="n">
         <v>0.000148</v>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr">
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>d’évaluation                                   1 300 252          342 222       assets</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>d’évaluation                                   1 300 252          342 222       assets</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="4" t="n">
+        <v>0.0009959999999999999</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>0.000207</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Exercice d’options                                  15 000                          -     Options exercised</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Frais d’émission d’actions                               (80 847)             (2 562)     Share issuance expenses</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" s="4" t="n">
+        <v>0.000438</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
         <is>
           <t>-</t>
         </is>
